--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$244</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8767" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8807" uniqueCount="899">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1725,6 +1725,9 @@
     <t>Procedure.code.coding.extension.value[x].code</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
   </si>
   <si>
@@ -2321,6 +2324,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.extension:Seitenlokalisation</t>
@@ -3098,7 +3117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN243"/>
+  <dimension ref="A1:AN244"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -5400,7 +5419,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>115</v>
@@ -5626,7 +5645,7 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
@@ -16548,7 +16567,7 @@
         <v>79</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>115</v>
@@ -16888,7 +16907,7 @@
         <v>79</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>115</v>
@@ -17112,7 +17131,7 @@
         <v>87</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>99</v>
@@ -17338,7 +17357,7 @@
         <v>79</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>115</v>
@@ -17454,7 +17473,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -17568,7 +17587,7 @@
         <v>87</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>99</v>
@@ -17622,7 +17641,9 @@
       <c r="M128" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N128" s="2"/>
+      <c r="N128" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="O128" t="s" s="2">
         <v>246</v>
       </c>
@@ -17682,7 +17703,7 @@
         <v>87</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>99</v>
@@ -17702,10 +17723,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17736,7 +17757,9 @@
       <c r="M129" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N129" s="2"/>
+      <c r="N129" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="O129" t="s" s="2">
         <v>253</v>
       </c>
@@ -17796,7 +17819,7 @@
         <v>87</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>99</v>
@@ -17816,10 +17839,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17912,7 +17935,7 @@
         <v>87</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>99</v>
@@ -17932,10 +17955,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17961,7 +17984,7 @@
         <v>128</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>229</v>
@@ -17977,7 +18000,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>77</v>
@@ -18028,7 +18051,7 @@
         <v>87</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>99</v>
@@ -18048,10 +18071,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18077,10 +18100,10 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>239</v>
@@ -18142,7 +18165,7 @@
         <v>87</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>99</v>
@@ -18162,10 +18185,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18191,12 +18214,14 @@
         <v>162</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M133" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N133" s="2"/>
+      <c r="N133" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="O133" t="s" s="2">
         <v>246</v>
       </c>
@@ -18211,7 +18236,7 @@
         <v>77</v>
       </c>
       <c r="T133" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="U133" t="s" s="2">
         <v>77</v>
@@ -18256,10 +18281,10 @@
         <v>87</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>77</v>
@@ -18276,10 +18301,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18310,7 +18335,9 @@
       <c r="M134" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N134" s="2"/>
+      <c r="N134" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="O134" t="s" s="2">
         <v>253</v>
       </c>
@@ -18370,7 +18397,7 @@
         <v>87</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>99</v>
@@ -18390,10 +18417,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18486,7 +18513,7 @@
         <v>87</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>99</v>
@@ -18506,7 +18533,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>512</v>
@@ -18575,7 +18602,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>77</v>
@@ -18622,7 +18649,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>522</v>
@@ -18734,7 +18761,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>524</v>
@@ -18848,10 +18875,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18964,10 +18991,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19078,10 +19105,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19192,10 +19219,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19306,10 +19333,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19422,10 +19449,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19538,14 +19565,14 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19564,13 +19591,13 @@
         <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19621,7 +19648,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>87</v>
@@ -19639,21 +19666,21 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19762,10 +19789,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19876,10 +19903,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19905,13 +19932,13 @@
         <v>101</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19961,7 +19988,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19970,7 +19997,7 @@
         <v>87</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>99</v>
@@ -19990,10 +20017,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20019,13 +20046,13 @@
         <v>128</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20054,10 +20081,10 @@
         <v>144</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>77</v>
@@ -20075,7 +20102,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -20104,10 +20131,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20133,13 +20160,13 @@
         <v>422</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20189,7 +20216,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -20218,10 +20245,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20247,13 +20274,13 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20303,7 +20330,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -20332,10 +20359,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20358,16 +20385,16 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20417,7 +20444,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -20435,21 +20462,21 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20558,10 +20585,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20672,10 +20699,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20701,13 +20728,13 @@
         <v>101</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -20757,7 +20784,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20766,7 +20793,7 @@
         <v>87</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>99</v>
@@ -20786,10 +20813,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20815,13 +20842,13 @@
         <v>128</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20850,10 +20877,10 @@
         <v>144</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>77</v>
@@ -20871,7 +20898,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20900,10 +20927,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20929,13 +20956,13 @@
         <v>422</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20985,7 +21012,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -21014,10 +21041,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21043,13 +21070,13 @@
         <v>101</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -21099,7 +21126,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -21128,10 +21155,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21154,16 +21181,16 @@
         <v>88</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21201,17 +21228,17 @@
         <v>77</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AC159" s="2"/>
       <c r="AD159" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -21229,21 +21256,21 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21352,10 +21379,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21466,10 +21493,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21495,13 +21522,13 @@
         <v>206</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21551,7 +21578,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -21560,13 +21587,13 @@
         <v>87</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>77</v>
@@ -21575,15 +21602,15 @@
         <v>77</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21609,20 +21636,20 @@
         <v>206</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q163" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="R163" t="s" s="2">
         <v>77</v>
@@ -21667,7 +21694,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21676,13 +21703,13 @@
         <v>87</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>77</v>
@@ -21691,18 +21718,18 @@
         <v>77</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>77</v>
@@ -21724,16 +21751,16 @@
         <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -21783,7 +21810,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21801,21 +21828,21 @@
         <v>77</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21924,10 +21951,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22038,10 +22065,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22067,13 +22094,13 @@
         <v>206</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22123,7 +22150,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -22132,7 +22159,7 @@
         <v>87</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>99</v>
@@ -22147,15 +22174,15 @@
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22181,20 +22208,20 @@
         <v>206</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q168" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="R168" t="s" s="2">
         <v>77</v>
@@ -22239,7 +22266,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -22248,7 +22275,7 @@
         <v>87</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>99</v>
@@ -22263,18 +22290,18 @@
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>77</v>
@@ -22299,13 +22326,13 @@
         <v>206</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -22355,7 +22382,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -22373,21 +22400,21 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22410,13 +22437,13 @@
         <v>88</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22467,7 +22494,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -22488,7 +22515,7 @@
         <v>77</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>77</v>
@@ -22496,10 +22523,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22522,13 +22549,13 @@
         <v>88</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -22579,7 +22606,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -22600,7 +22627,7 @@
         <v>77</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>77</v>
@@ -22608,10 +22635,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22634,13 +22661,13 @@
         <v>88</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -22691,7 +22718,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22709,7 +22736,7 @@
         <v>77</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>77</v>
@@ -22720,10 +22747,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22832,10 +22859,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22946,14 +22973,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -22975,10 +23002,10 @@
         <v>107</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>110</v>
@@ -23033,7 +23060,7 @@
         <v>77</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -23062,10 +23089,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23091,14 +23118,14 @@
         <v>275</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>77</v>
@@ -23126,10 +23153,10 @@
         <v>152</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>77</v>
@@ -23147,7 +23174,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -23165,21 +23192,21 @@
         <v>77</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23202,17 +23229,17 @@
         <v>88</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -23261,7 +23288,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>87</v>
@@ -23279,21 +23306,21 @@
         <v>77</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23316,17 +23343,17 @@
         <v>77</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>77</v>
@@ -23375,7 +23402,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
@@ -23404,10 +23431,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23430,17 +23457,17 @@
         <v>88</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
@@ -23489,7 +23516,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -23510,7 +23537,7 @@
         <v>77</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>77</v>
@@ -23518,10 +23545,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23547,13 +23574,13 @@
         <v>275</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -23582,10 +23609,10 @@
         <v>152</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>77</v>
@@ -23603,7 +23630,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -23621,10 +23648,10 @@
         <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>77</v>
@@ -23632,10 +23659,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23658,16 +23685,16 @@
         <v>88</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -23717,7 +23744,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -23735,10 +23762,10 @@
         <v>77</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>77</v>
@@ -23746,10 +23773,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23775,13 +23802,13 @@
         <v>275</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -23811,7 +23838,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>77</v>
@@ -23829,7 +23856,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>78</v>
@@ -23853,15 +23880,15 @@
         <v>77</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23970,10 +23997,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24082,15 +24109,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B185" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="B185" t="s" s="2">
-        <v>741</v>
-      </c>
       <c r="C185" t="s" s="2">
-        <v>526</v>
+        <v>744</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>77</v>
@@ -24103,7 +24130,7 @@
         <v>87</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>77</v>
@@ -24112,13 +24139,13 @@
         <v>77</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -24196,14 +24223,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="186" hidden="true">
+    <row r="186">
       <c r="A186" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="C186" s="2"/>
+        <v>742</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="D186" t="s" s="2">
         <v>77</v>
       </c>
@@ -24215,7 +24244,7 @@
         <v>87</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>77</v>
@@ -24224,13 +24253,13 @@
         <v>77</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>101</v>
+        <v>749</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>102</v>
+        <v>750</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>103</v>
+        <v>751</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24281,19 +24310,19 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>77</v>
@@ -24310,10 +24339,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24324,7 +24353,7 @@
         <v>78</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>77</v>
@@ -24336,13 +24365,13 @@
         <v>77</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -24381,31 +24410,31 @@
         <v>77</v>
       </c>
       <c r="AB187" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC187" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE187" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>77</v>
@@ -24422,10 +24451,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24433,10 +24462,10 @@
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>77</v>
@@ -24448,24 +24477,22 @@
         <v>77</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q188" s="2"/>
       <c r="R188" t="s" s="2">
-        <v>752</v>
+        <v>77</v>
       </c>
       <c r="S188" t="s" s="2">
         <v>77</v>
@@ -24495,31 +24522,31 @@
         <v>77</v>
       </c>
       <c r="AB188" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC188" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE188" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="AG188" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>77</v>
@@ -24536,10 +24563,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24547,7 +24574,7 @@
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G189" t="s" s="2">
         <v>87</v>
@@ -24562,22 +24589,24 @@
         <v>77</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>275</v>
+        <v>128</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>755</v>
+        <v>199</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="N189" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q189" s="2"/>
       <c r="R189" t="s" s="2">
-        <v>77</v>
+        <v>758</v>
       </c>
       <c r="S189" t="s" s="2">
         <v>77</v>
@@ -24595,11 +24624,13 @@
         <v>77</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y189" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z189" t="s" s="2">
-        <v>757</v>
+        <v>77</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>77</v>
@@ -24617,10 +24648,10 @@
         <v>77</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH189" t="s" s="2">
         <v>87</v>
@@ -24629,7 +24660,7 @@
         <v>77</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>77</v>
@@ -24646,10 +24677,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24672,13 +24703,13 @@
         <v>77</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>102</v>
+        <v>761</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>103</v>
+        <v>762</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -24705,13 +24736,11 @@
         <v>77</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>77</v>
+        <v>763</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>77</v>
@@ -24729,7 +24758,7 @@
         <v>77</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>78</v>
@@ -24741,7 +24770,7 @@
         <v>77</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>77</v>
@@ -24758,21 +24787,21 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>77</v>
@@ -24784,17 +24813,15 @@
         <v>77</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>77</v>
@@ -24831,31 +24858,31 @@
         <v>77</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC191" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD191" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>77</v>
@@ -24872,14 +24899,14 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
@@ -24895,23 +24922,21 @@
         <v>77</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>764</v>
+        <v>108</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>765</v>
+        <v>109</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>77</v>
       </c>
@@ -24947,19 +24972,19 @@
         <v>77</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>78</v>
@@ -24971,7 +24996,7 @@
         <v>77</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>77</v>
@@ -24983,15 +25008,15 @@
         <v>77</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25002,7 +25027,7 @@
         <v>78</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>77</v>
@@ -25011,19 +25036,23 @@
         <v>77</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>102</v>
+        <v>770</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N193" s="2"/>
-      <c r="O193" s="2"/>
+        <v>771</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>77</v>
       </c>
@@ -25071,19 +25100,19 @@
         <v>77</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>77</v>
@@ -25095,26 +25124,26 @@
         <v>77</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>77</v>
@@ -25126,17 +25155,15 @@
         <v>77</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N194" s="2"/>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
         <v>77</v>
@@ -25173,31 +25200,31 @@
         <v>77</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC194" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE194" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>77</v>
@@ -25214,21 +25241,21 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>77</v>
@@ -25237,23 +25264,21 @@
         <v>77</v>
       </c>
       <c r="J195" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>77</v>
       </c>
@@ -25289,31 +25314,31 @@
         <v>77</v>
       </c>
       <c r="AB195" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC195" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE195" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>77</v>
@@ -25325,15 +25350,15 @@
         <v>77</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25356,18 +25381,20 @@
         <v>88</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O196" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O196" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P196" t="s" s="2">
         <v>77</v>
       </c>
@@ -25415,7 +25442,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -25439,15 +25466,15 @@
         <v>77</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25470,18 +25497,18 @@
         <v>88</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N197" s="2"/>
-      <c r="O197" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N197" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>77</v>
       </c>
@@ -25529,7 +25556,7 @@
         <v>77</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -25544,7 +25571,7 @@
         <v>99</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>776</v>
+        <v>77</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>77</v>
@@ -25553,15 +25580,15 @@
         <v>77</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25584,17 +25611,17 @@
         <v>88</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>77</v>
@@ -25643,7 +25670,7 @@
         <v>77</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>78</v>
@@ -25658,7 +25685,7 @@
         <v>99</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>77</v>
+        <v>782</v>
       </c>
       <c r="AL198" t="s" s="2">
         <v>77</v>
@@ -25667,15 +25694,15 @@
         <v>77</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25698,19 +25725,17 @@
         <v>88</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N199" s="2"/>
       <c r="O199" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>77</v>
@@ -25759,7 +25784,7 @@
         <v>77</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>78</v>
@@ -25783,15 +25808,15 @@
         <v>77</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25814,19 +25839,19 @@
         <v>88</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>77</v>
@@ -25875,7 +25900,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -25899,15 +25924,15 @@
         <v>77</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25918,10 +25943,10 @@
         <v>78</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H201" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I201" t="s" s="2">
         <v>77</v>
@@ -25930,19 +25955,19 @@
         <v>88</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>784</v>
+        <v>305</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>785</v>
+        <v>306</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>77</v>
@@ -25979,23 +26004,25 @@
         <v>77</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="AC201" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC201" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD201" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>77</v>
@@ -26013,15 +26040,15 @@
         <v>77</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>286</v>
+        <v>310</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26032,28 +26059,32 @@
         <v>78</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>102</v>
+        <v>790</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N202" s="2"/>
-      <c r="O202" s="2"/>
+        <v>791</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O202" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P202" t="s" s="2">
         <v>77</v>
       </c>
@@ -26089,31 +26120,29 @@
         <v>77</v>
       </c>
       <c r="AB202" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC202" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>792</v>
+      </c>
+      <c r="AC202" s="2"/>
       <c r="AD202" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE202" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ202" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK202" t="s" s="2">
         <v>77</v>
@@ -26125,26 +26154,26 @@
         <v>77</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>77</v>
@@ -26156,17 +26185,15 @@
         <v>77</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N203" s="2"/>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
         <v>77</v>
@@ -26203,31 +26230,31 @@
         <v>77</v>
       </c>
       <c r="AB203" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC203" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD203" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE203" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>77</v>
@@ -26244,21 +26271,21 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>77</v>
@@ -26267,23 +26294,21 @@
         <v>77</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>77</v>
       </c>
@@ -26319,31 +26344,31 @@
         <v>77</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>77</v>
@@ -26355,15 +26380,15 @@
         <v>77</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26386,18 +26411,20 @@
         <v>88</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O205" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O205" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P205" t="s" s="2">
         <v>77</v>
       </c>
@@ -26445,7 +26472,7 @@
         <v>77</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>78</v>
@@ -26469,15 +26496,15 @@
         <v>77</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26500,18 +26527,18 @@
         <v>88</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N206" s="2"/>
-      <c r="O206" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N206" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>77</v>
       </c>
@@ -26559,7 +26586,7 @@
         <v>77</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>78</v>
@@ -26574,7 +26601,7 @@
         <v>99</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>792</v>
+        <v>77</v>
       </c>
       <c r="AL206" t="s" s="2">
         <v>77</v>
@@ -26583,15 +26610,15 @@
         <v>77</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -26614,17 +26641,17 @@
         <v>88</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>77</v>
@@ -26673,7 +26700,7 @@
         <v>77</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>78</v>
@@ -26688,7 +26715,7 @@
         <v>99</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>77</v>
+        <v>798</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>77</v>
@@ -26697,15 +26724,15 @@
         <v>77</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -26728,19 +26755,17 @@
         <v>88</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>77</v>
@@ -26789,7 +26814,7 @@
         <v>77</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>78</v>
@@ -26813,19 +26838,17 @@
         <v>77</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="C209" t="s" s="2">
-        <v>796</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
         <v>77</v>
       </c>
@@ -26837,7 +26860,7 @@
         <v>87</v>
       </c>
       <c r="H209" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I209" t="s" s="2">
         <v>77</v>
@@ -26846,19 +26869,19 @@
         <v>88</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>481</v>
+        <v>259</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>482</v>
+        <v>260</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>77</v>
@@ -26907,13 +26930,13 @@
         <v>77</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>77</v>
@@ -26931,17 +26954,19 @@
         <v>77</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>286</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="210" hidden="true">
+    <row r="210">
       <c r="A210" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="C210" s="2"/>
+        <v>789</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>802</v>
+      </c>
       <c r="D210" t="s" s="2">
         <v>77</v>
       </c>
@@ -26953,25 +26978,29 @@
         <v>87</v>
       </c>
       <c r="H210" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I210" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>102</v>
+        <v>481</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N210" s="2"/>
-      <c r="O210" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>77</v>
       </c>
@@ -27019,19 +27048,19 @@
         <v>77</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>77</v>
@@ -27043,26 +27072,26 @@
         <v>77</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>77</v>
@@ -27074,17 +27103,15 @@
         <v>77</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>77</v>
@@ -27121,31 +27148,31 @@
         <v>77</v>
       </c>
       <c r="AB211" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC211" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD211" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE211" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>77</v>
@@ -27160,48 +27187,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H212" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I212" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O212" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>77</v>
       </c>
@@ -27210,7 +27235,7 @@
         <v>77</v>
       </c>
       <c r="S212" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="T212" t="s" s="2">
         <v>77</v>
@@ -27237,31 +27262,31 @@
         <v>77</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>77</v>
@@ -27273,15 +27298,15 @@
         <v>77</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27289,7 +27314,7 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G213" t="s" s="2">
         <v>87</v>
@@ -27304,18 +27329,20 @@
         <v>88</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O213" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O213" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>77</v>
       </c>
@@ -27324,7 +27351,7 @@
         <v>77</v>
       </c>
       <c r="S213" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="T213" t="s" s="2">
         <v>77</v>
@@ -27363,7 +27390,7 @@
         <v>77</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>78</v>
@@ -27387,15 +27414,15 @@
         <v>77</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -27403,7 +27430,7 @@
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G214" t="s" s="2">
         <v>87</v>
@@ -27418,18 +27445,18 @@
         <v>88</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N214" s="2"/>
-      <c r="O214" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>77</v>
       </c>
@@ -27477,7 +27504,7 @@
         <v>77</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>78</v>
@@ -27501,15 +27528,15 @@
         <v>77</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="215" hidden="true">
+    <row r="215">
       <c r="A215" t="s" s="2">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -27517,13 +27544,13 @@
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G215" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>77</v>
@@ -27532,17 +27559,17 @@
         <v>88</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>77</v>
@@ -27591,7 +27618,7 @@
         <v>77</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>78</v>
@@ -27615,15 +27642,15 @@
         <v>77</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -27646,19 +27673,17 @@
         <v>88</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N216" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>77</v>
@@ -27707,7 +27732,7 @@
         <v>77</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>78</v>
@@ -27731,15 +27756,15 @@
         <v>77</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -27762,19 +27787,19 @@
         <v>88</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>77</v>
@@ -27823,7 +27848,7 @@
         <v>77</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>78</v>
@@ -27847,15 +27872,15 @@
         <v>77</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -27878,18 +27903,20 @@
         <v>88</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>275</v>
+        <v>101</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>806</v>
+        <v>305</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>807</v>
+        <v>306</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="O218" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O218" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P218" t="s" s="2">
         <v>77</v>
       </c>
@@ -27913,13 +27940,13 @@
         <v>77</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>809</v>
+        <v>77</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>810</v>
+        <v>77</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>77</v>
@@ -27937,7 +27964,7 @@
         <v>77</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>805</v>
+        <v>309</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>78</v>
@@ -27961,7 +27988,7 @@
         <v>77</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>77</v>
+        <v>310</v>
       </c>
     </row>
     <row r="219" hidden="true">
@@ -27980,7 +28007,7 @@
         <v>78</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>77</v>
@@ -27989,19 +28016,19 @@
         <v>77</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K219" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L219" t="s" s="2">
         <v>812</v>
       </c>
-      <c r="L219" t="s" s="2">
+      <c r="M219" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M219" t="s" s="2">
+      <c r="N219" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="N219" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -28027,13 +28054,13 @@
         <v>77</v>
       </c>
       <c r="X219" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y219" t="s" s="2">
-        <v>77</v>
+        <v>815</v>
       </c>
       <c r="Z219" t="s" s="2">
-        <v>77</v>
+        <v>816</v>
       </c>
       <c r="AA219" t="s" s="2">
         <v>77</v>
@@ -28057,7 +28084,7 @@
         <v>78</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>77</v>
@@ -28080,10 +28107,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28106,16 +28133,16 @@
         <v>77</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>275</v>
+        <v>818</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
@@ -28141,13 +28168,13 @@
         <v>77</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>820</v>
+        <v>77</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>821</v>
+        <v>77</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>77</v>
@@ -28165,7 +28192,7 @@
         <v>77</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>78</v>
@@ -28220,18 +28247,18 @@
         <v>77</v>
       </c>
       <c r="K221" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L221" t="s" s="2">
         <v>823</v>
       </c>
-      <c r="L221" t="s" s="2">
+      <c r="M221" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="M221" t="s" s="2">
+      <c r="N221" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="N221" s="2"/>
-      <c r="O221" t="s" s="2">
-        <v>826</v>
-      </c>
+      <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>77</v>
       </c>
@@ -28255,13 +28282,13 @@
         <v>77</v>
       </c>
       <c r="X221" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y221" t="s" s="2">
-        <v>77</v>
+        <v>826</v>
       </c>
       <c r="Z221" t="s" s="2">
-        <v>77</v>
+        <v>827</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>77</v>
@@ -28308,10 +28335,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -28334,16 +28361,18 @@
         <v>77</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>275</v>
+        <v>829</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N222" s="2"/>
-      <c r="O222" s="2"/>
+      <c r="O222" t="s" s="2">
+        <v>832</v>
+      </c>
       <c r="P222" t="s" s="2">
         <v>77</v>
       </c>
@@ -28367,13 +28396,13 @@
         <v>77</v>
       </c>
       <c r="X222" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y222" t="s" s="2">
-        <v>830</v>
+        <v>77</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>831</v>
+        <v>77</v>
       </c>
       <c r="AA222" t="s" s="2">
         <v>77</v>
@@ -28391,7 +28420,7 @@
         <v>77</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>78</v>
@@ -28418,12 +28447,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -28437,7 +28466,7 @@
         <v>79</v>
       </c>
       <c r="H223" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I223" t="s" s="2">
         <v>77</v>
@@ -28446,7 +28475,7 @@
         <v>77</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>833</v>
+        <v>275</v>
       </c>
       <c r="L223" t="s" s="2">
         <v>834</v>
@@ -28479,13 +28508,13 @@
         <v>77</v>
       </c>
       <c r="X223" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>77</v>
+        <v>836</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>77</v>
+        <v>837</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>77</v>
@@ -28503,7 +28532,7 @@
         <v>77</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>78</v>
@@ -28521,16 +28550,16 @@
         <v>77</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>836</v>
+        <v>77</v>
       </c>
       <c r="AM223" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>837</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="224" hidden="true">
+    <row r="224">
       <c r="A224" t="s" s="2">
         <v>838</v>
       </c>
@@ -28549,7 +28578,7 @@
         <v>79</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>77</v>
@@ -28558,13 +28587,13 @@
         <v>77</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>682</v>
+        <v>839</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -28633,21 +28662,21 @@
         <v>77</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>77</v>
+        <v>842</v>
       </c>
       <c r="AM224" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>77</v>
+        <v>843</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -28658,7 +28687,7 @@
         <v>78</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>77</v>
@@ -28670,13 +28699,13 @@
         <v>77</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>101</v>
+        <v>683</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>102</v>
+        <v>845</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>103</v>
+        <v>846</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -28727,19 +28756,19 @@
         <v>77</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>104</v>
+        <v>844</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI225" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ225" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK225" t="s" s="2">
         <v>77</v>
@@ -28756,21 +28785,21 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H226" t="s" s="2">
         <v>77</v>
@@ -28782,17 +28811,15 @@
         <v>77</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N226" s="2"/>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>77</v>
@@ -28841,19 +28868,19 @@
         <v>77</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI226" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK226" t="s" s="2">
         <v>77</v>
@@ -28870,14 +28897,14 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>689</v>
+        <v>106</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
@@ -28890,26 +28917,24 @@
         <v>77</v>
       </c>
       <c r="I227" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K227" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>690</v>
+        <v>108</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>691</v>
+        <v>109</v>
       </c>
       <c r="N227" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O227" t="s" s="2">
-        <v>419</v>
-      </c>
+      <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
         <v>77</v>
       </c>
@@ -28957,7 +28982,7 @@
         <v>77</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>692</v>
+        <v>114</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>78</v>
@@ -28986,42 +29011,46 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>77</v>
+        <v>690</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I228" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>275</v>
+        <v>107</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>845</v>
+        <v>691</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="N228" s="2"/>
-      <c r="O228" s="2"/>
+        <v>692</v>
+      </c>
+      <c r="N228" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O228" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P228" t="s" s="2">
         <v>77</v>
       </c>
@@ -29045,13 +29074,13 @@
         <v>77</v>
       </c>
       <c r="X228" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>847</v>
+        <v>77</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>848</v>
+        <v>77</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>77</v>
@@ -29069,19 +29098,19 @@
         <v>77</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>844</v>
+        <v>693</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>77</v>
@@ -29098,10 +29127,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29109,7 +29138,7 @@
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G229" t="s" s="2">
         <v>87</v>
@@ -29124,7 +29153,7 @@
         <v>77</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>850</v>
+        <v>275</v>
       </c>
       <c r="L229" t="s" s="2">
         <v>851</v>
@@ -29157,13 +29186,13 @@
         <v>77</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>77</v>
+        <v>853</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>77</v>
+        <v>854</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>77</v>
@@ -29181,10 +29210,10 @@
         <v>77</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AG229" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH229" t="s" s="2">
         <v>87</v>
@@ -29210,10 +29239,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29221,10 +29250,10 @@
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>77</v>
@@ -29236,20 +29265,16 @@
         <v>77</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="O230" t="s" s="2">
         <v>858</v>
       </c>
+      <c r="N230" s="2"/>
+      <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>77</v>
       </c>
@@ -29297,13 +29322,13 @@
         <v>77</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>77</v>
@@ -29343,7 +29368,7 @@
         <v>79</v>
       </c>
       <c r="H231" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I231" t="s" s="2">
         <v>77</v>
@@ -29352,18 +29377,20 @@
         <v>77</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>275</v>
+        <v>860</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="O231" s="2"/>
+        <v>863</v>
+      </c>
+      <c r="O231" t="s" s="2">
+        <v>864</v>
+      </c>
       <c r="P231" t="s" s="2">
         <v>77</v>
       </c>
@@ -29387,26 +29414,28 @@
         <v>77</v>
       </c>
       <c r="X231" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y231" t="s" s="2">
-        <v>862</v>
+        <v>77</v>
       </c>
       <c r="Z231" t="s" s="2">
-        <v>863</v>
+        <v>77</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB231" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="AC231" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC231" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD231" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE231" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF231" t="s" s="2">
         <v>859</v>
@@ -29436,16 +29465,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
         <v>865</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="C232" t="s" s="2">
-        <v>866</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
         <v>77</v>
       </c>
@@ -29454,7 +29481,7 @@
         <v>78</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H232" t="s" s="2">
         <v>88</v>
@@ -29475,7 +29502,7 @@
         <v>867</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -29501,29 +29528,29 @@
         <v>77</v>
       </c>
       <c r="X232" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y232" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="Y232" t="s" s="2">
+        <v>868</v>
+      </c>
       <c r="Z232" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB232" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>870</v>
+      </c>
+      <c r="AC232" s="2"/>
       <c r="AD232" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE232" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>78</v>
@@ -29550,14 +29577,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="233" hidden="true">
+    <row r="233">
       <c r="A233" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="C233" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="C233" t="s" s="2">
+        <v>872</v>
+      </c>
       <c r="D233" t="s" s="2">
         <v>77</v>
       </c>
@@ -29569,7 +29598,7 @@
         <v>87</v>
       </c>
       <c r="H233" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I233" t="s" s="2">
         <v>77</v>
@@ -29578,15 +29607,17 @@
         <v>77</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>102</v>
+        <v>872</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N233" s="2"/>
+        <v>873</v>
+      </c>
+      <c r="N233" t="s" s="2">
+        <v>863</v>
+      </c>
       <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
         <v>77</v>
@@ -29611,13 +29642,11 @@
         <v>77</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y233" s="2"/>
       <c r="Z233" t="s" s="2">
-        <v>77</v>
+        <v>874</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>77</v>
@@ -29635,19 +29664,19 @@
         <v>77</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>104</v>
+        <v>865</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI233" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>77</v>
@@ -29664,21 +29693,21 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>77</v>
@@ -29690,17 +29719,15 @@
         <v>77</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N234" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N234" s="2"/>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
         <v>77</v>
@@ -29737,31 +29764,31 @@
         <v>77</v>
       </c>
       <c r="AB234" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC234" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD234" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE234" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH234" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI234" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK234" t="s" s="2">
         <v>77</v>
@@ -29778,14 +29805,14 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
@@ -29801,23 +29828,21 @@
         <v>77</v>
       </c>
       <c r="J235" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>281</v>
+        <v>108</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>282</v>
+        <v>109</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O235" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
         <v>77</v>
       </c>
@@ -29853,19 +29878,19 @@
         <v>77</v>
       </c>
       <c r="AB235" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC235" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD235" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE235" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>78</v>
@@ -29877,7 +29902,7 @@
         <v>77</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK235" t="s" s="2">
         <v>77</v>
@@ -29889,15 +29914,15 @@
         <v>77</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -29908,7 +29933,7 @@
         <v>78</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>77</v>
@@ -29917,19 +29942,23 @@
         <v>77</v>
       </c>
       <c r="J236" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>102</v>
+        <v>281</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N236" s="2"/>
-      <c r="O236" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N236" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O236" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P236" t="s" s="2">
         <v>77</v>
       </c>
@@ -29977,19 +30006,19 @@
         <v>77</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK236" t="s" s="2">
         <v>77</v>
@@ -30001,26 +30030,26 @@
         <v>77</v>
       </c>
       <c r="AN236" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>77</v>
@@ -30032,17 +30061,15 @@
         <v>77</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N237" s="2"/>
       <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
         <v>77</v>
@@ -30079,31 +30106,31 @@
         <v>77</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC237" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD237" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE237" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK237" t="s" s="2">
         <v>77</v>
@@ -30118,48 +30145,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H238" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I238" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J238" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O238" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>77</v>
       </c>
@@ -30168,7 +30193,7 @@
         <v>77</v>
       </c>
       <c r="S238" t="s" s="2">
-        <v>881</v>
+        <v>77</v>
       </c>
       <c r="T238" t="s" s="2">
         <v>77</v>
@@ -30195,31 +30220,31 @@
         <v>77</v>
       </c>
       <c r="AB238" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC238" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD238" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE238" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK238" t="s" s="2">
         <v>77</v>
@@ -30231,15 +30256,15 @@
         <v>77</v>
       </c>
       <c r="AN238" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="239" hidden="true">
+    <row r="239">
       <c r="A239" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -30247,13 +30272,13 @@
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G239" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H239" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I239" t="s" s="2">
         <v>77</v>
@@ -30262,18 +30287,20 @@
         <v>88</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O239" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O239" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P239" t="s" s="2">
         <v>77</v>
       </c>
@@ -30282,7 +30309,7 @@
         <v>77</v>
       </c>
       <c r="S239" t="s" s="2">
-        <v>77</v>
+        <v>887</v>
       </c>
       <c r="T239" t="s" s="2">
         <v>77</v>
@@ -30321,7 +30348,7 @@
         <v>77</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>78</v>
@@ -30345,15 +30372,15 @@
         <v>77</v>
       </c>
       <c r="AN239" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -30361,13 +30388,13 @@
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G240" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H240" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I240" t="s" s="2">
         <v>77</v>
@@ -30376,18 +30403,18 @@
         <v>88</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N240" s="2"/>
-      <c r="O240" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N240" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>77</v>
       </c>
@@ -30435,7 +30462,7 @@
         <v>77</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>78</v>
@@ -30450,7 +30477,7 @@
         <v>99</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>886</v>
+        <v>77</v>
       </c>
       <c r="AL240" t="s" s="2">
         <v>77</v>
@@ -30459,15 +30486,15 @@
         <v>77</v>
       </c>
       <c r="AN240" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="241" hidden="true">
+    <row r="241">
       <c r="A241" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -30475,13 +30502,13 @@
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G241" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H241" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I241" t="s" s="2">
         <v>77</v>
@@ -30490,17 +30517,17 @@
         <v>88</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>77</v>
@@ -30549,7 +30576,7 @@
         <v>77</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>78</v>
@@ -30564,7 +30591,7 @@
         <v>99</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>77</v>
+        <v>892</v>
       </c>
       <c r="AL241" t="s" s="2">
         <v>77</v>
@@ -30573,15 +30600,15 @@
         <v>77</v>
       </c>
       <c r="AN241" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -30604,19 +30631,17 @@
         <v>88</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>77</v>
@@ -30665,7 +30690,7 @@
         <v>77</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>78</v>
@@ -30689,15 +30714,15 @@
         <v>77</v>
       </c>
       <c r="AN242" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -30720,19 +30745,19 @@
         <v>88</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>77</v>
@@ -30781,7 +30806,7 @@
         <v>77</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>78</v>
@@ -30805,11 +30830,127 @@
         <v>77</v>
       </c>
       <c r="AN243" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="244" hidden="true">
+      <c r="A244" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="C244" s="2"/>
+      <c r="D244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E244" s="2"/>
+      <c r="F244" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G244" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J244" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K244" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L244" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M244" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N244" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O244" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="P244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q244" s="2"/>
+      <c r="R244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF244" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG244" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH244" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ244" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM244" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN244" t="s" s="2">
         <v>310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN243">
+  <autoFilter ref="A1:AN244">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -30819,7 +30960,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI242">
+  <conditionalFormatting sqref="A2:AI243">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-nuklearmedizin.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
